--- a/output/04_こども計画.xlsx
+++ b/output/04_こども計画.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="表紙・凡例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="差込データ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="共通項目定義" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="部品マスタ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="レイアウト一覧" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="デザインルール" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="使い分けガイド" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表紙・凡例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="差込データ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共通項目定義" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部品マスタ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="レイアウト一覧" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="デザインルール" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い分けガイド" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'差込データ'!$A$1:$L$10</definedName>

--- a/output/04_こども計画.xlsx
+++ b/output/04_こども計画.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>部品名／主な用途／使用頻度（★）</t>
+          <t>部品名／主な用途／使用頻度（）</t>
         </is>
       </c>
       <c r="C15" s="8" t="n"/>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>★1〜5</t>
+          <t>1〜5</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
